--- a/data/trans_dic/IP12B$oido-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,19</t>
+          <t>0,0; 45,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,92</t>
+          <t>0,0; 43,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,89</t>
+          <t>0,0; 38,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,88</t>
+          <t>0,0; 21,97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,23</t>
+          <t>0,0; 37,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,94</t>
+          <t>0,0; 19,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,46</t>
+          <t>0,0; 53,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,65</t>
+          <t>0,0; 43,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,0</t>
+          <t>0,0; 37,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,52</t>
+          <t>0,0; 41,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,76</t>
+          <t>0,0; 59,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 36,16</t>
+          <t>3,87; 34,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 36,64</t>
+          <t>4,4; 36,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,66</t>
+          <t>0,0; 20,02</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,24</t>
+          <t>0,0; 36,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,6</t>
+          <t>0,0; 57,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,93</t>
+          <t>0,0; 20,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,05</t>
+          <t>0,0; 40,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,3</t>
+          <t>0,0; 72,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,83</t>
+          <t>0,0; 56,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,85; 49,86</t>
+          <t>6,83; 44,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,69</t>
+          <t>0,0; 39,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,69</t>
+          <t>0,0; 50,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,13</t>
+          <t>0,0; 69,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,28</t>
+          <t>0,0; 52,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,03</t>
+          <t>0,0; 55,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,85</t>
+          <t>0,0; 36,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,11</t>
+          <t>0,0; 27,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,33</t>
+          <t>0,0; 39,43</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,94</t>
+          <t>0,0; 41,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,82</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,45</t>
+          <t>0,0; 25,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,57</t>
+          <t>0,0; 29,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,35</t>
+          <t>0,0; 19,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,67</t>
+          <t>0,0; 25,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,64</t>
+          <t>0,0; 14,55</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,43</t>
+          <t>1,17; 10,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,36</t>
+          <t>3,48; 15,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,18</t>
+          <t>2,1; 12,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,29</t>
+          <t>1,46; 13,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,11</t>
+          <t>2,62; 14,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,86</t>
+          <t>1,17; 10,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,77</t>
+          <t>2,02; 8,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,9</t>
+          <t>4,02; 12,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,52; 10,2</t>
+          <t>2,19; 9,28</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3720</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4409</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5068</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4241</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2994</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3022</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3442</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3728</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3707</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3790</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>567; 5068</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>655; 5378</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3908</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2584</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3011</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2528</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1483</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3770</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2866</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>700; 4541</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2995</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3021</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2799</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3166</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2700</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4242</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3656</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4257</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2835</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3349</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3521</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3096</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3777</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4404</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3468</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4915</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>9216</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>513; 4685</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2134; 9388</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1157; 6853</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>681; 6145</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1667; 8940</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>561; 5237</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1827; 8113</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>5025; 15153</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2257; 9558</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$oido-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,21</t>
+          <t>0,0; 44,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,5</t>
+          <t>0,0; 41,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,47</t>
+          <t>0,0; 36,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,97</t>
+          <t>0,0; 21,8</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,32</t>
+          <t>0,0; 46,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,75</t>
+          <t>0,0; 23,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,36</t>
+          <t>0,0; 47,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,67</t>
+          <t>0,0; 45,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,67</t>
+          <t>0,0; 34,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,5</t>
+          <t>0,0; 43,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,66</t>
+          <t>0,0; 59,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 34,66</t>
+          <t>4,08; 33,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 36,12</t>
+          <t>4,45; 38,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,02</t>
+          <t>0,0; 18,73</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,17</t>
+          <t>0,0; 35,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,28</t>
+          <t>0,0; 56,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,4</t>
+          <t>0,0; 27,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,16</t>
+          <t>0,0; 48,32</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,2</t>
+          <t>0,0; 71,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,93</t>
+          <t>0,0; 57,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 44,27</t>
+          <t>6,9; 50,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,55</t>
+          <t>0,0; 45,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,76</t>
+          <t>0,0; 49,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,42</t>
+          <t>0,0; 57,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,7</t>
+          <t>0,0; 56,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,52</t>
+          <t>0,0; 36,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,7</t>
+          <t>0,0; 23,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,43</t>
+          <t>0,0; 43,96</t>
         </is>
       </c>
     </row>
@@ -1453,22 +1453,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,21</t>
+          <t>0,0; 41,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 25,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,34</t>
+          <t>0,0; 25,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,91</t>
+          <t>0,0; 29,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,17 +1478,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,18</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,56</t>
+          <t>0,0; 25,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,55</t>
+          <t>0,0; 16,45</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,68</t>
+          <t>1,18; 11,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,32</t>
+          <t>3,4; 15,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,43</t>
+          <t>2,05; 12,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,16</t>
+          <t>1,49; 14,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,07</t>
+          <t>2,38; 13,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,94</t>
+          <t>1,16; 10,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,96</t>
+          <t>1,92; 10,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,14</t>
+          <t>3,98; 11,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,28</t>
+          <t>2,51; 9,52</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3720</t>
+          <t>0; 3695</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>0; 4173</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>0; 4822</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4241</t>
+          <t>0; 4208</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2994</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3022</t>
+          <t>0; 3642</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,27 +2350,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3442</t>
+          <t>0; 3071</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3728</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3707</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3391</t>
+          <t>0; 3595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3790</t>
+          <t>0; 3805</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2380,17 +2380,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>567; 5068</t>
+          <t>597; 4946</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>655; 5378</t>
+          <t>663; 5750</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3908</t>
+          <t>0; 3656</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>0; 2997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2584</t>
+          <t>0; 2568</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3011</t>
+          <t>0; 4050</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2528</t>
+          <t>0; 3042</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3770</t>
+          <t>0; 3753</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2866</t>
+          <t>0; 2880</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>700; 4541</t>
+          <t>708; 5191</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2995</t>
+          <t>0; 3408</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 2963</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,27 +2859,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3166</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2700</t>
+          <t>0; 2754</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4242</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>0; 3054</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>0; 4746</t>
         </is>
       </c>
     </row>
@@ -3007,22 +3007,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2835</t>
+          <t>0; 2847</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>0; 3398</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 3554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3096</t>
+          <t>0; 3063</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3777</t>
+          <t>0; 3084</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4404</t>
+          <t>0; 4427</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3468</t>
+          <t>0; 3922</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>513; 4685</t>
+          <t>519; 5013</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2134; 9388</t>
+          <t>2083; 9514</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1157; 6853</t>
+          <t>1132; 7010</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>681; 6145</t>
+          <t>697; 6587</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1667; 8940</t>
+          <t>1511; 8885</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>561; 5237</t>
+          <t>556; 5178</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1827; 8113</t>
+          <t>1742; 9092</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5025; 15153</t>
+          <t>4975; 14624</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2257; 9558</t>
+          <t>2582; 9799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$oido-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,12 +630,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 39,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,61</t>
+          <t>0,0; 33,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,8</t>
+          <t>0,0; 21,88</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,11%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,8</t>
+          <t>0,0; 23,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,6</t>
+          <t>0,0; 45,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,25</t>
+          <t>0,0; 56,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,99</t>
+          <t>0,0; 46,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,9</t>
+          <t>0,0; 44,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 32,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 33,83</t>
+          <t>3,65; 36,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 38,62</t>
+          <t>4,15; 36,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,73</t>
+          <t>0,0; 18,66</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,46%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,23%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 35,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,44</t>
+          <t>0,0; 20,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,32</t>
+          <t>0,0; 48,05</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>28,39%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,86</t>
+          <t>0,0; 57,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,21</t>
+          <t>0,0; 71,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 50,61</t>
+          <t>6,85; 49,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>12,95%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,01</t>
+          <t>0,0; 69,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,79</t>
+          <t>0,0; 63,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,22</t>
+          <t>0,0; 40,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,81</t>
+          <t>0,0; 50,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,67</t>
+          <t>0,0; 36,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,14</t>
+          <t>0,0; 28,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,96</t>
+          <t>0,0; 39,33</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>10,67%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>8,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,38</t>
+          <t>0,0; 29,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,59</t>
+          <t>0,0; 41,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 19,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,69</t>
+          <t>0,0; 25,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,45</t>
+          <t>0,0; 16,64</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>8,02%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,77%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,42</t>
+          <t>1,46; 12,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,52</t>
+          <t>2,35; 14,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 12,72</t>
+          <t>1,2; 11,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,1</t>
+          <t>1,18; 10,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,98</t>
+          <t>3,52; 15,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,82</t>
+          <t>2,07; 12,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 10,04</t>
+          <t>2,2; 9,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,71</t>
+          <t>4,33; 11,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,52</t>
+          <t>2,52; 10,2</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>942</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3695</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4173</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4822</t>
+          <t>0; 4464</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 4223</t>
         </is>
       </c>
     </row>
@@ -2086,22 +2086,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,22 +2139,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>731</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2987</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3642</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2254,22 +2254,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1259</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>715</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>0; 3720</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 3606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>0; 2997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3805</t>
+          <t>0; 3812</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3149</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>597; 4946</t>
+          <t>533; 5288</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>663; 5750</t>
+          <t>618; 5456</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>0; 3643</t>
         </is>
       </c>
     </row>
@@ -2412,27 +2412,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2465,27 +2465,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>597</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2568</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2957</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2508</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 3088</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3042</t>
+          <t>0; 3025</t>
         </is>
       </c>
     </row>
@@ -2575,22 +2575,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1483</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3753</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2880</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>708; 5191</t>
+          <t>702; 5114</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>771</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3408</t>
+          <t>0; 2796</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2963</t>
+          <t>0; 3055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2799</t>
+          <t>0; 3081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3479</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2754</t>
+          <t>0; 3017</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 4281</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3054</t>
+          <t>0; 3710</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4746</t>
+          <t>0; 4247</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1100</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2980</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2847</t>
+          <t>0; 3061</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3398</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3554</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3063</t>
+          <t>0; 2886</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3365</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3084</t>
+          <t>0; 3812</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4427</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3967</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1767</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>4915</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>3183</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4301</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>519; 5013</t>
+          <t>682; 5742</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2083; 9514</t>
+          <t>1494; 8966</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1132; 7010</t>
+          <t>573; 5674</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>697; 6587</t>
+          <t>517; 4578</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1511; 8885</t>
+          <t>2155; 9416</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>556; 5178</t>
+          <t>1139; 6714</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1742; 9092</t>
+          <t>1988; 8848</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>4975; 14624</t>
+          <t>5406; 14851</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2582; 9799</t>
+          <t>2598; 10505</t>
         </is>
       </c>
     </row>
